--- a/outputs/analysis/data_quality_report.xlsx
+++ b/outputs/analysis/data_quality_report.xlsx
@@ -111,16 +111,16 @@
     <t>Share of supplied engagement-event rows; delivered-email counts are unavailable.</t>
   </si>
   <si>
-    <t>web_sessions</t>
-  </si>
-  <si>
-    <t>domain_matched_sessions</t>
+    <t>web_event_rows</t>
+  </si>
+  <si>
+    <t>domain_matched_event_rows</t>
   </si>
   <si>
     <t>unique_matched_domains</t>
   </si>
   <si>
-    <t>matched_sessions_with_utm</t>
+    <t>matched_event_rows_with_utm</t>
   </si>
   <si>
     <t>source</t>
@@ -535,10 +535,10 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>3288</v>
+        <v>3245</v>
       </c>
       <c r="C2">
-        <v>3288</v>
+        <v>3245</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -555,13 +555,13 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>2841</v>
+        <v>2834</v>
       </c>
       <c r="C3">
-        <v>3288</v>
+        <v>3245</v>
       </c>
       <c r="D3">
-        <v>0.8640510948905109</v>
+        <v>0.8733436055469954</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -575,13 +575,13 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>447</v>
+        <v>411</v>
       </c>
       <c r="C4">
-        <v>3288</v>
+        <v>3245</v>
       </c>
       <c r="D4">
-        <v>0.135948905109489</v>
+        <v>0.1266563944530046</v>
       </c>
       <c r="E4" t="s">
         <v>12</v>
@@ -595,13 +595,13 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>1773</v>
+        <v>1741</v>
       </c>
       <c r="C5">
-        <v>3288</v>
+        <v>3245</v>
       </c>
       <c r="D5">
-        <v>0.5392335766423357</v>
+        <v>0.536517719568567</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
@@ -615,13 +615,13 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C6">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="D6">
-        <v>0.6533084808946877</v>
+        <v>0.6532710280373831</v>
       </c>
       <c r="E6" t="s">
         <v>14</v>
@@ -635,13 +635,13 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>3169</v>
+        <v>3130</v>
       </c>
       <c r="C7">
-        <v>3288</v>
+        <v>3245</v>
       </c>
       <c r="D7">
-        <v>0.9638077858880778</v>
+        <v>0.9645608628659477</v>
       </c>
       <c r="E7" t="s">
         <v>15</v>
@@ -885,10 +885,10 @@
         <v>16421</v>
       </c>
       <c r="B2">
-        <v>3288</v>
+        <v>3245</v>
       </c>
       <c r="C2">
-        <v>13133</v>
+        <v>13176</v>
       </c>
     </row>
   </sheetData>
